--- a/data/processed/harmonization/Physical__Clay_content/10.15485_2283432/10.15485_2283432_soil_Physical__Clay_content.xlsx
+++ b/data/processed/harmonization/Physical__Clay_content/10.15485_2283432/10.15485_2283432_soil_Physical__Clay_content.xlsx
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>187946:0-20</t>
+          <t>0-20:187946</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>187947:20-40</t>
+          <t>20-40:187947</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -634,12 +634,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>187948:40-60</t>
+          <t>40-60:187948</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>187949:60-100</t>
+          <t>60-100:187949</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>187950:0-20</t>
+          <t>0-20:187950</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>188051:20-40</t>
+          <t>20-40:188051</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>187951:40-60</t>
+          <t>40-60:187951</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>187952:60-100</t>
+          <t>60-100:187952</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>187955:0-20</t>
+          <t>0-20:187955</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>187956:20-40</t>
+          <t>20-40:187956</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>187957:40-60</t>
+          <t>40-60:187957</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>188054:60-100</t>
+          <t>60-100:188054</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>187953:0-20</t>
+          <t>0-20:187953</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>187954:20-40</t>
+          <t>20-40:187954</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>188052:40-60</t>
+          <t>40-60:188052</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>188053:60-100</t>
+          <t>60-100:188053</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
